--- a/Data_Students/Data_2025_2024.xlsx
+++ b/Data_Students/Data_2025_2024.xlsx
@@ -656,37 +656,37 @@
     <t>IBAT College Dublin</t>
   </si>
   <si>
-    <t>Agriculture and Environment</t>
-  </si>
-  <si>
-    <t>Architecture and Urban Studies</t>
-  </si>
-  <si>
-    <t>Business and Management</t>
-  </si>
-  <si>
-    <t>Humanities and Arts</t>
-  </si>
-  <si>
-    <t>International Relations and Policy</t>
-  </si>
-  <si>
-    <t>Education and Social Sciences</t>
-  </si>
-  <si>
-    <t>Food and Culinary</t>
-  </si>
-  <si>
-    <t>Life Sciences and Health</t>
-  </si>
-  <si>
-    <t>Engineering and Technology</t>
-  </si>
-  <si>
-    <t>Data and Analytics</t>
-  </si>
-  <si>
     <t>Major_General</t>
+  </si>
+  <si>
+    <t>Agriculture or Environment</t>
+  </si>
+  <si>
+    <t>Architecture or Urban Studies</t>
+  </si>
+  <si>
+    <t>Business, Finance, or Management</t>
+  </si>
+  <si>
+    <t>Humanities or Arts</t>
+  </si>
+  <si>
+    <t>International Relations or Policy</t>
+  </si>
+  <si>
+    <t>Education or Social Sciences</t>
+  </si>
+  <si>
+    <t>Food or Culinary</t>
+  </si>
+  <si>
+    <t>Engineering or Technology</t>
+  </si>
+  <si>
+    <t>Data or Analytics</t>
+  </si>
+  <si>
+    <t>Health or Life Sciences</t>
   </si>
 </sst>
 </file>
@@ -1031,7 +1031,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="F1" s="2" t="s">
         <v>4</v>
@@ -1060,7 +1060,7 @@
         <v>53</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>156</v>
@@ -1089,7 +1089,7 @@
         <v>10</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F3" s="2" t="s">
         <v>11</v>
@@ -1118,7 +1118,7 @@
         <v>50</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F4" s="2" t="s">
         <v>30</v>
@@ -1147,7 +1147,7 @@
         <v>10</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>15</v>
@@ -1176,7 +1176,7 @@
         <v>29</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>157</v>
@@ -1205,7 +1205,7 @@
         <v>10</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>16</v>
@@ -1234,7 +1234,7 @@
         <v>10</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>158</v>
@@ -1263,7 +1263,7 @@
         <v>10</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F9" s="2" t="s">
         <v>17</v>
@@ -1292,7 +1292,7 @@
         <v>53</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F10" s="2" t="s">
         <v>19</v>
@@ -1321,7 +1321,7 @@
         <v>10</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F11" s="2" t="s">
         <v>20</v>
@@ -1350,7 +1350,7 @@
         <v>10</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>22</v>
@@ -1379,7 +1379,7 @@
         <v>10</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F13" s="2" t="s">
         <v>25</v>
@@ -1408,7 +1408,7 @@
         <v>10</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F14" s="2" t="s">
         <v>26</v>
@@ -1466,7 +1466,7 @@
         <v>29</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F16" s="2" t="s">
         <v>30</v>
@@ -1495,7 +1495,7 @@
         <v>29</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F17" s="2" t="s">
         <v>31</v>
@@ -1553,7 +1553,7 @@
         <v>10</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F19" s="1" t="s">
         <v>160</v>
@@ -1582,7 +1582,7 @@
         <v>10</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F20" s="2" t="s">
         <v>34</v>
@@ -1611,7 +1611,7 @@
         <v>35</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F21" s="2" t="s">
         <v>36</v>
@@ -1640,7 +1640,7 @@
         <v>203</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F22" s="2" t="s">
         <v>37</v>
@@ -1669,7 +1669,7 @@
         <v>53</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F23" s="1" t="s">
         <v>96</v>
@@ -1698,7 +1698,7 @@
         <v>10</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>161</v>
@@ -1727,7 +1727,7 @@
         <v>10</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F25" s="2" t="s">
         <v>40</v>
@@ -1756,7 +1756,7 @@
         <v>66</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F26" s="2" t="s">
         <v>41</v>
@@ -1785,7 +1785,7 @@
         <v>10</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F27" s="2" t="s">
         <v>42</v>
@@ -1814,7 +1814,7 @@
         <v>10</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F28" s="2" t="s">
         <v>43</v>
@@ -1843,7 +1843,7 @@
         <v>203</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F29" s="2" t="s">
         <v>45</v>
@@ -1872,7 +1872,7 @@
         <v>10</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F30" s="2" t="s">
         <v>47</v>
@@ -1901,7 +1901,7 @@
         <v>10</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F31" s="2" t="s">
         <v>48</v>
@@ -1930,7 +1930,7 @@
         <v>10</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F32" s="2" t="s">
         <v>49</v>
@@ -1988,7 +1988,7 @@
         <v>53</v>
       </c>
       <c r="E34" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F34" s="2" t="s">
         <v>54</v>
@@ -2017,7 +2017,7 @@
         <v>53</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F35" s="1" t="s">
         <v>162</v>
@@ -2046,7 +2046,7 @@
         <v>84</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F36" s="1" t="s">
         <v>163</v>
@@ -2075,7 +2075,7 @@
         <v>206</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F37" s="2" t="s">
         <v>56</v>
@@ -2104,7 +2104,7 @@
         <v>58</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F38" s="1" t="s">
         <v>59</v>
@@ -2133,7 +2133,7 @@
         <v>29</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F39" s="1" t="s">
         <v>164</v>
@@ -2162,7 +2162,7 @@
         <v>29</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F40" s="2" t="s">
         <v>60</v>
@@ -2191,7 +2191,7 @@
         <v>10</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F41" s="1" t="s">
         <v>61</v>
@@ -2249,7 +2249,7 @@
         <v>10</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F43" s="1" t="s">
         <v>165</v>
@@ -2278,7 +2278,7 @@
         <v>66</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F44" s="2" t="s">
         <v>63</v>
@@ -2336,7 +2336,7 @@
         <v>204</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F46" s="1" t="s">
         <v>167</v>
@@ -2365,7 +2365,7 @@
         <v>53</v>
       </c>
       <c r="E47" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>153</v>
@@ -2394,7 +2394,7 @@
         <v>66</v>
       </c>
       <c r="E48" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>67</v>
@@ -2423,7 +2423,7 @@
         <v>29</v>
       </c>
       <c r="E49" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>68</v>
@@ -2452,7 +2452,7 @@
         <v>35</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F50" s="2" t="s">
         <v>70</v>
@@ -2481,7 +2481,7 @@
         <v>53</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F51" s="1" t="s">
         <v>168</v>
@@ -2510,7 +2510,7 @@
         <v>10</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F52" s="2" t="s">
         <v>71</v>
@@ -2539,7 +2539,7 @@
         <v>10</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F53" s="1" t="s">
         <v>99</v>
@@ -2568,7 +2568,7 @@
         <v>73</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F54" s="2" t="s">
         <v>74</v>
@@ -2597,7 +2597,7 @@
         <v>205</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F55" s="2" t="s">
         <v>77</v>
@@ -2626,7 +2626,7 @@
         <v>29</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F56" s="1" t="s">
         <v>169</v>
@@ -2655,7 +2655,7 @@
         <v>53</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F57" s="1" t="s">
         <v>145</v>
@@ -2684,7 +2684,7 @@
         <v>29</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F58" s="1" t="s">
         <v>170</v>
@@ -2713,7 +2713,7 @@
         <v>10</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F59" s="2" t="s">
         <v>79</v>
@@ -2742,7 +2742,7 @@
         <v>10</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F60" s="2" t="s">
         <v>80</v>
@@ -2771,7 +2771,7 @@
         <v>206</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F61" s="2" t="s">
         <v>81</v>
@@ -2800,7 +2800,7 @@
         <v>35</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F62" s="1" t="s">
         <v>45</v>
@@ -2858,7 +2858,7 @@
         <v>35</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F64" s="1" t="s">
         <v>171</v>
@@ -2916,7 +2916,7 @@
         <v>10</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>83</v>
@@ -2945,7 +2945,7 @@
         <v>29</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F67" s="1" t="s">
         <v>173</v>
@@ -2974,7 +2974,7 @@
         <v>84</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F68" s="2" t="s">
         <v>85</v>
@@ -3003,7 +3003,7 @@
         <v>195</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F69" s="1" t="s">
         <v>174</v>
@@ -3032,7 +3032,7 @@
         <v>29</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F70" s="1" t="s">
         <v>176</v>
@@ -3061,7 +3061,7 @@
         <v>35</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F71" s="2" t="s">
         <v>86</v>
@@ -3090,7 +3090,7 @@
         <v>29</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F72" s="2" t="s">
         <v>87</v>
@@ -3119,7 +3119,7 @@
         <v>50</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>88</v>
@@ -3148,7 +3148,7 @@
         <v>53</v>
       </c>
       <c r="E74" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F74" s="2" t="s">
         <v>154</v>
@@ -3177,7 +3177,7 @@
         <v>35</v>
       </c>
       <c r="E75" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F75" s="2" t="s">
         <v>89</v>
@@ -3206,7 +3206,7 @@
         <v>207</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F76" s="2" t="s">
         <v>91</v>
@@ -3264,7 +3264,7 @@
         <v>10</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F78" s="2" t="s">
         <v>94</v>
@@ -3293,7 +3293,7 @@
         <v>206</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F79" s="1" t="s">
         <v>177</v>
@@ -3322,7 +3322,7 @@
         <v>10</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F80" s="2" t="s">
         <v>95</v>
@@ -3351,7 +3351,7 @@
         <v>53</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F81" s="2" t="s">
         <v>96</v>
@@ -3380,7 +3380,7 @@
         <v>10</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F82" s="2" t="s">
         <v>98</v>
@@ -3409,7 +3409,7 @@
         <v>10</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F83" s="2" t="s">
         <v>100</v>
@@ -3438,7 +3438,7 @@
         <v>181</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F84" s="2" t="s">
         <v>155</v>
@@ -3467,7 +3467,7 @@
         <v>10</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F85" s="2" t="s">
         <v>102</v>
@@ -3496,7 +3496,7 @@
         <v>10</v>
       </c>
       <c r="E86" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F86" s="1" t="s">
         <v>178</v>
@@ -3525,7 +3525,7 @@
         <v>66</v>
       </c>
       <c r="E87" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F87" s="2" t="s">
         <v>25</v>
@@ -3554,7 +3554,7 @@
         <v>10</v>
       </c>
       <c r="E88" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F88" s="2" t="s">
         <v>152</v>
@@ -3641,7 +3641,7 @@
         <v>181</v>
       </c>
       <c r="E91" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F91" s="1" t="s">
         <v>182</v>
@@ -3670,7 +3670,7 @@
         <v>35</v>
       </c>
       <c r="E92" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F92" s="2" t="s">
         <v>104</v>
@@ -3699,7 +3699,7 @@
         <v>10</v>
       </c>
       <c r="E93" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F93" s="2" t="s">
         <v>106</v>
@@ -3728,7 +3728,7 @@
         <v>53</v>
       </c>
       <c r="E94" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F94" s="2" t="s">
         <v>107</v>
@@ -3815,7 +3815,7 @@
         <v>10</v>
       </c>
       <c r="E97" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F97" s="2" t="s">
         <v>86</v>
@@ -3873,7 +3873,7 @@
         <v>53</v>
       </c>
       <c r="E99" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F99" s="2" t="s">
         <v>110</v>
@@ -3902,7 +3902,7 @@
         <v>53</v>
       </c>
       <c r="E100" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F100" s="2" t="s">
         <v>111</v>
@@ -3931,7 +3931,7 @@
         <v>35</v>
       </c>
       <c r="E101" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F101" s="1" t="s">
         <v>96</v>
@@ -3960,7 +3960,7 @@
         <v>10</v>
       </c>
       <c r="E102" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F102" s="2" t="s">
         <v>114</v>
@@ -3989,7 +3989,7 @@
         <v>35</v>
       </c>
       <c r="E103" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F103" s="1" t="s">
         <v>184</v>
@@ -4018,7 +4018,7 @@
         <v>29</v>
       </c>
       <c r="E104" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F104" s="1" t="s">
         <v>185</v>
@@ -4047,7 +4047,7 @@
         <v>53</v>
       </c>
       <c r="E105" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F105" s="2" t="s">
         <v>112</v>
@@ -4076,7 +4076,7 @@
         <v>10</v>
       </c>
       <c r="E106" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F106" s="2" t="s">
         <v>115</v>
@@ -4105,7 +4105,7 @@
         <v>10</v>
       </c>
       <c r="E107" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F107" s="1" t="s">
         <v>148</v>
@@ -4134,7 +4134,7 @@
         <v>10</v>
       </c>
       <c r="E108" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F108" s="2" t="s">
         <v>116</v>
@@ -4163,7 +4163,7 @@
         <v>35</v>
       </c>
       <c r="E109" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F109" s="1" t="s">
         <v>186</v>
@@ -4192,7 +4192,7 @@
         <v>66</v>
       </c>
       <c r="E110" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F110" s="2" t="s">
         <v>117</v>
@@ -4221,7 +4221,7 @@
         <v>118</v>
       </c>
       <c r="E111" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F111" s="2" t="s">
         <v>119</v>
@@ -4250,7 +4250,7 @@
         <v>35</v>
       </c>
       <c r="E112" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F112" s="1" t="s">
         <v>187</v>
@@ -4279,7 +4279,7 @@
         <v>206</v>
       </c>
       <c r="E113" s="3" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="F113" s="2" t="s">
         <v>122</v>
@@ -4337,7 +4337,7 @@
         <v>66</v>
       </c>
       <c r="E115" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F115" s="2" t="s">
         <v>124</v>
@@ -4366,7 +4366,7 @@
         <v>53</v>
       </c>
       <c r="E116" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F116" s="1" t="s">
         <v>123</v>
@@ -4395,7 +4395,7 @@
         <v>128</v>
       </c>
       <c r="E117" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F117" s="2" t="s">
         <v>129</v>
@@ -4424,7 +4424,7 @@
         <v>208</v>
       </c>
       <c r="E118" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F118" s="2" t="s">
         <v>125</v>
@@ -4453,7 +4453,7 @@
         <v>126</v>
       </c>
       <c r="E119" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F119" s="2" t="s">
         <v>127</v>
@@ -4482,7 +4482,7 @@
         <v>10</v>
       </c>
       <c r="E120" s="3" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="F120" s="2" t="s">
         <v>130</v>
@@ -4511,7 +4511,7 @@
         <v>10</v>
       </c>
       <c r="E121" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F121" s="1" t="s">
         <v>189</v>
@@ -4569,7 +4569,7 @@
         <v>10</v>
       </c>
       <c r="E123" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F123" s="2" t="s">
         <v>132</v>
@@ -4627,7 +4627,7 @@
         <v>53</v>
       </c>
       <c r="E125" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F125" s="2" t="s">
         <v>135</v>
@@ -4656,7 +4656,7 @@
         <v>53</v>
       </c>
       <c r="E126" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F126" s="2" t="s">
         <v>136</v>
@@ -4685,7 +4685,7 @@
         <v>35</v>
       </c>
       <c r="E127" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F127" s="1" t="s">
         <v>190</v>
@@ -4714,7 +4714,7 @@
         <v>10</v>
       </c>
       <c r="E128" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F128" s="1" t="s">
         <v>191</v>
@@ -4743,7 +4743,7 @@
         <v>29</v>
       </c>
       <c r="E129" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F129" s="1" t="s">
         <v>192</v>
@@ -4772,7 +4772,7 @@
         <v>35</v>
       </c>
       <c r="E130" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F130" s="2" t="s">
         <v>137</v>
@@ -4801,7 +4801,7 @@
         <v>35</v>
       </c>
       <c r="E131" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F131" s="2" t="s">
         <v>127</v>
@@ -4830,7 +4830,7 @@
         <v>10</v>
       </c>
       <c r="E132" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F132" s="1" t="s">
         <v>193</v>
@@ -4859,7 +4859,7 @@
         <v>66</v>
       </c>
       <c r="E133" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F133" s="1" t="s">
         <v>124</v>
@@ -4888,7 +4888,7 @@
         <v>10</v>
       </c>
       <c r="E134" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F134" s="2" t="s">
         <v>16</v>
@@ -4917,7 +4917,7 @@
         <v>35</v>
       </c>
       <c r="E135" s="3" t="s">
-        <v>216</v>
+        <v>219</v>
       </c>
       <c r="F135" s="2" t="s">
         <v>139</v>
@@ -4946,7 +4946,7 @@
         <v>10</v>
       </c>
       <c r="E136" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F136" s="2" t="s">
         <v>140</v>
@@ -5004,7 +5004,7 @@
         <v>53</v>
       </c>
       <c r="E138" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F138" s="2" t="s">
         <v>143</v>
@@ -5033,7 +5033,7 @@
         <v>29</v>
       </c>
       <c r="E139" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F139" s="1" t="s">
         <v>142</v>
@@ -5062,7 +5062,7 @@
         <v>53</v>
       </c>
       <c r="E140" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F140" s="2" t="s">
         <v>111</v>
@@ -5091,7 +5091,7 @@
         <v>53</v>
       </c>
       <c r="E141" s="3" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="F141" s="1" t="s">
         <v>197</v>
@@ -5120,7 +5120,7 @@
         <v>53</v>
       </c>
       <c r="E142" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F142" s="2" t="s">
         <v>145</v>
@@ -5178,7 +5178,7 @@
         <v>53</v>
       </c>
       <c r="E144" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F144" s="1" t="s">
         <v>198</v>
@@ -5207,7 +5207,7 @@
         <v>10</v>
       </c>
       <c r="E145" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F145" s="2" t="s">
         <v>146</v>
@@ -5236,7 +5236,7 @@
         <v>29</v>
       </c>
       <c r="E146" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F146" s="1" t="s">
         <v>199</v>
@@ -5294,7 +5294,7 @@
         <v>10</v>
       </c>
       <c r="E148" s="3" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="F148" s="2" t="s">
         <v>88</v>
@@ -5323,7 +5323,7 @@
         <v>29</v>
       </c>
       <c r="E149" s="3" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="F149" s="2" t="s">
         <v>150</v>
@@ -5352,7 +5352,7 @@
         <v>29</v>
       </c>
       <c r="E150" s="3" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="F150" s="1" t="s">
         <v>201</v>
@@ -5410,7 +5410,7 @@
         <v>10</v>
       </c>
       <c r="E152" s="3" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="F152" s="2" t="s">
         <v>149</v>
